--- a/output/pdf_financials_xlsx/QBTQ.xlsx
+++ b/output/pdf_financials_xlsx/QBTQ.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.006641</v>
+        <v>0.207662</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.70079</v>
+        <v>3.320047</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.006641</v>
+        <v>-0.207662</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.70079</v>
+        <v>-3.320047</v>
       </c>
     </row>
     <row r="12">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.341637</v>
       </c>
     </row>
     <row r="35">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.341637</v>
       </c>
     </row>
     <row r="37">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.488539</v>
+        <v>0.146902</v>
       </c>
     </row>
     <row r="49">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3632,14 +3632,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>-0.207662</v>
+        <v>0.207662</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-3.320047</v>
+        <v>3.320047</v>
       </c>
     </row>
     <row r="52">

--- a/output/pdf_financials_xlsx/QBTQ.xlsx
+++ b/output/pdf_financials_xlsx/QBTQ.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.006641</v>
+        <v>0.144592</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.70079</v>
+        <v>1.19598</v>
       </c>
     </row>
     <row r="8">
@@ -3134,7 +3134,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -3496,7 +3500,11 @@
           <t>Management and directors’ fees (Note 6)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>0.09909900000000001</v>
       </c>
@@ -3520,7 +3528,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.038852</v>
       </c>
